--- a/Lab_4/data/partB/param_optimization_process/v150_k20_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k20_s100_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
-        <v>7</v>
-      </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -573,13 +573,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -594,25 +594,25 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>25</v>
@@ -683,40 +683,40 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -726,43 +726,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -842,34 +842,34 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1068,19 +1068,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,31 +1090,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1145,19 +1145,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1215,28 +1215,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
         <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22585,7 +22585,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
